--- a/results/04_final_refined_daily_hydroclimate_data/203/Precipitation_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Precipitation_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -413,8 +413,8 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>0</v>
+      <c r="D2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -427,8 +427,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>0</v>
+      <c r="D3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -441,8 +441,8 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>0</v>
+      <c r="D4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5">
-        <v>0</v>
+      <c r="D5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -469,8 +469,8 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6">
-        <v>30.9</v>
+      <c r="D6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -497,8 +497,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -511,8 +511,8 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>4</v>
+      <c r="D9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -525,8 +525,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="D10">
+        <v>11.1</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -539,8 +539,8 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>4</v>
+      <c r="D11">
+        <v>25.7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>23.7</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -637,8 +637,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
-        <v>4</v>
+      <c r="D18">
+        <v>6.7</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -651,8 +651,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
-        <v>4</v>
+      <c r="D19">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -665,8 +665,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>4</v>
+      <c r="D20">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -679,8 +679,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
-        <v>4</v>
+      <c r="D21">
+        <v>8.4</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -693,8 +693,8 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
-        <v>4</v>
+      <c r="D22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -707,8 +707,8 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
-        <v>4</v>
+      <c r="D23">
+        <v>4.8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -721,8 +721,8 @@
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
-        <v>4</v>
+      <c r="D24">
+        <v>0.2</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -735,8 +735,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25" t="s">
-        <v>4</v>
+      <c r="D25">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -749,8 +749,8 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
-        <v>4</v>
+      <c r="D26">
+        <v>30.6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -847,8 +847,8 @@
       <c r="C33">
         <v>1</v>
       </c>
-      <c r="D33">
-        <v>0</v>
+      <c r="D33" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -861,8 +861,8 @@
       <c r="C34">
         <v>2</v>
       </c>
-      <c r="D34">
-        <v>1.9</v>
+      <c r="D34" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -875,8 +875,8 @@
       <c r="C35">
         <v>3</v>
       </c>
-      <c r="D35">
-        <v>0</v>
+      <c r="D35" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -889,8 +889,8 @@
       <c r="C36">
         <v>4</v>
       </c>
-      <c r="D36">
-        <v>0.1</v>
+      <c r="D36" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -903,8 +903,8 @@
       <c r="C37">
         <v>5</v>
       </c>
-      <c r="D37">
-        <v>0</v>
+      <c r="D37" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -917,8 +917,8 @@
       <c r="C38">
         <v>6</v>
       </c>
-      <c r="D38" t="s">
-        <v>4</v>
+      <c r="D38">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -931,8 +931,8 @@
       <c r="C39">
         <v>7</v>
       </c>
-      <c r="D39" t="s">
-        <v>4</v>
+      <c r="D39">
+        <v>4.8</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -945,8 +945,8 @@
       <c r="C40">
         <v>8</v>
       </c>
-      <c r="D40" t="s">
-        <v>4</v>
+      <c r="D40">
+        <v>11.6</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -959,8 +959,8 @@
       <c r="C41">
         <v>9</v>
       </c>
-      <c r="D41" t="s">
-        <v>4</v>
+      <c r="D41">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -973,8 +973,8 @@
       <c r="C42">
         <v>10</v>
       </c>
-      <c r="D42" t="s">
-        <v>4</v>
+      <c r="D42">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1057,8 +1057,8 @@
       <c r="C48">
         <v>16</v>
       </c>
-      <c r="D48" t="s">
-        <v>4</v>
+      <c r="D48">
+        <v>5.6</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1071,8 +1071,8 @@
       <c r="C49">
         <v>17</v>
       </c>
-      <c r="D49" t="s">
-        <v>4</v>
+      <c r="D49">
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1085,8 +1085,8 @@
       <c r="C50">
         <v>18</v>
       </c>
-      <c r="D50" t="s">
-        <v>4</v>
+      <c r="D50">
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1099,8 +1099,8 @@
       <c r="C51">
         <v>19</v>
       </c>
-      <c r="D51" t="s">
-        <v>4</v>
+      <c r="D51">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1113,8 +1113,8 @@
       <c r="C52">
         <v>20</v>
       </c>
-      <c r="D52" t="s">
-        <v>4</v>
+      <c r="D52">
+        <v>18.1</v>
       </c>
     </row>
     <row r="53" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Precipitation_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Precipitation_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -413,8 +413,8 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
+      <c r="D2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -427,8 +427,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>4</v>
+      <c r="D3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -441,8 +441,8 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
+      <c r="D4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>4</v>
+      <c r="D5">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -469,8 +469,8 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
-        <v>4</v>
+      <c r="D6">
+        <v>30.9</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -847,8 +847,8 @@
       <c r="C33">
         <v>1</v>
       </c>
-      <c r="D33" t="s">
-        <v>4</v>
+      <c r="D33">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -861,8 +861,8 @@
       <c r="C34">
         <v>2</v>
       </c>
-      <c r="D34" t="s">
-        <v>4</v>
+      <c r="D34">
+        <v>1.9</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -875,8 +875,8 @@
       <c r="C35">
         <v>3</v>
       </c>
-      <c r="D35" t="s">
-        <v>4</v>
+      <c r="D35">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -889,8 +889,8 @@
       <c r="C36">
         <v>4</v>
       </c>
-      <c r="D36" t="s">
-        <v>4</v>
+      <c r="D36">
+        <v>0.1</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -903,8 +903,8 @@
       <c r="C37">
         <v>5</v>
       </c>
-      <c r="D37" t="s">
-        <v>4</v>
+      <c r="D37">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1127,8 +1127,8 @@
       <c r="C53">
         <v>21</v>
       </c>
-      <c r="D53" t="s">
-        <v>4</v>
+      <c r="D53">
+        <v>3.4</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1141,8 +1141,8 @@
       <c r="C54">
         <v>22</v>
       </c>
-      <c r="D54" t="s">
-        <v>4</v>
+      <c r="D54">
+        <v>4.5</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1155,8 +1155,8 @@
       <c r="C55">
         <v>23</v>
       </c>
-      <c r="D55" t="s">
-        <v>4</v>
+      <c r="D55">
+        <v>5.9</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1169,8 +1169,8 @@
       <c r="C56">
         <v>24</v>
       </c>
-      <c r="D56" t="s">
-        <v>4</v>
+      <c r="D56">
+        <v>2.8</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1183,8 +1183,8 @@
       <c r="C57">
         <v>25</v>
       </c>
-      <c r="D57" t="s">
-        <v>4</v>
+      <c r="D57">
+        <v>1.3</v>
       </c>
     </row>
     <row r="58" spans="1:4">
